--- a/planos_empresas/plano_empresa_11112.xlsx
+++ b/planos_empresas/plano_empresa_11112.xlsx
@@ -413,9 +413,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>010501 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>070101 - Engenharia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>072003 - Levantamentos topográficos e congêneres.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>110201 - Vigilância, segurança ou monitoramento de bens, pessoas e semoventes.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>170601 - Propaganda e publicidade, inclusive promoção de vendas, planejamento de campanhas ou sistemas de publicidade, elaboração de desenhos, textos e demais materiais publicitários.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>172501 - Inserção de textos, desenhos e outros materiais de propaganda e publicidade, em qualquer meio (exceto em livros, jornais, periódicos e nas modalidades de serviços de radiodifusão sonora e de sons e imagens de recepção livre e gratuita).</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>320101 - Serviços de desenhos técnicos.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>